--- a/data/trans_orig/P45C_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76928</t>
+          <t>75951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111165</t>
+          <t>112066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72881</t>
+          <t>71436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107692</t>
+          <t>107033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156931</t>
+          <t>156364</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207312</t>
+          <t>208801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>917286</t>
+          <t>916385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>951523</t>
+          <t>952500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1205179</t>
+          <t>1205838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1239990</t>
+          <t>1241435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2134011</t>
+          <t>2132522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2184392</t>
+          <t>2184959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>288578</t>
+          <t>288815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353554</t>
+          <t>353665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>241086</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>213227</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>270300</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>17,08%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>241086</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>216055</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>274002</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>558</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519328</t>
+          <t>517212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>602998</t>
+          <t>606109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1336263</t>
+          <t>1336152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1401239</t>
+          <t>1401002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,47 +1204,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>82,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1341643</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1312429</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1369502</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>82,92%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1341643</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1308727</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1366674</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,77%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>82,69%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2669549</t>
+          <t>2666438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2753219</t>
+          <t>2755335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>82223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118314</t>
+          <t>119051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71437</t>
+          <t>73779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105462</t>
+          <t>108491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165005</t>
+          <t>164580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216973</t>
+          <t>212663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432282</t>
+          <t>431545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>469565</t>
+          <t>468373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>369937</t>
+          <t>366908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>403962</t>
+          <t>401620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>809021</t>
+          <t>813331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860989</t>
+          <t>861414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>470835</t>
+          <t>471293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>553488</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>380482</t>
+          <t>384174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456084</t>
+          <t>457603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>873613</t>
+          <t>873195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>990516</t>
+          <t>991115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89517</t>
+          <t>91824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130676</t>
+          <t>130761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105109</t>
+          <t>106729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149384</t>
+          <t>149603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205853</t>
+          <t>208697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>263920</t>
+          <t>268024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>835714</t>
+          <t>835629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>876873</t>
+          <t>874566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1172543</t>
+          <t>1172324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1216818</t>
+          <t>1215198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2024398</t>
+          <t>2020294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2082465</t>
+          <t>2079621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>350895</t>
+          <t>348782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>422342</t>
+          <t>420695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>246891</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310948</t>
+          <t>309650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>614769</t>
+          <t>614010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>710319</t>
+          <t>707542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1528089</t>
+          <t>1529736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1599536</t>
+          <t>1601649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1430804</t>
+          <t>1432102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1494861</t>
+          <t>1494693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2981865</t>
+          <t>2984642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3077415</t>
+          <t>3078174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88384</t>
+          <t>87865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125024</t>
+          <t>123623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54871</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86831</t>
+          <t>87731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149991</t>
+          <t>151710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200780</t>
+          <t>203051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350205</t>
+          <t>351606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>386845</t>
+          <t>387364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>368837</t>
+          <t>367937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400797</t>
+          <t>400849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>730117</t>
+          <t>727846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>780906</t>
+          <t>779187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>554891</t>
+          <t>554770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>645801</t>
+          <t>642474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>432906</t>
+          <t>427052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>517701</t>
+          <t>512158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1019911</t>
+          <t>1007952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1140073</t>
+          <t>1133797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2746249</t>
+          <t>2749576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2837159</t>
+          <t>2837280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3001647</t>
+          <t>3007190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3086442</t>
+          <t>3092296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5771326</t>
+          <t>5777602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5891488</t>
+          <t>5903447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35786</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63236</t>
+          <t>65019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48416</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79970</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92694</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133986</t>
+          <t>133675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683070</t>
+          <t>681287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>710520</t>
+          <t>709808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>905021</t>
+          <t>904666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>936575</t>
+          <t>936340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1597311</t>
+          <t>1597622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1638603</t>
+          <t>1639644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>284670</t>
+          <t>284002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>358126</t>
+          <t>355385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>282961</t>
+          <t>282702</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>348839</t>
+          <t>346519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>589183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680466</t>
+          <t>680347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1702846</t>
+          <t>1705587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1776302</t>
+          <t>1776970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1629035</t>
+          <t>1631355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1694913</t>
+          <t>1695172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3358380</t>
+          <t>3358499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3449266</t>
+          <t>3449663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66683</t>
+          <t>68052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105017</t>
+          <t>104015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80269</t>
+          <t>80249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117779</t>
+          <t>116969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157960</t>
+          <t>161519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210572</t>
+          <t>211068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436245</t>
+          <t>437247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474579</t>
+          <t>473210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425123</t>
+          <t>425933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462633</t>
+          <t>462653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>873592</t>
+          <t>873096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926204</t>
+          <t>922645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>414105</t>
+          <t>415727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>494647</t>
+          <t>497857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>434059</t>
+          <t>433287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>516821</t>
+          <t>513680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>879125</t>
+          <t>868504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>987222</t>
+          <t>985985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2853893</t>
+          <t>2850683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2934435</t>
+          <t>2932813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2988946</t>
+          <t>2992087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3071708</t>
+          <t>3072480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5867084</t>
+          <t>5868321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5975181</t>
+          <t>5985802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62381</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93541</t>
+          <t>94919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57527</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82715</t>
+          <t>82092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129088</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168087</t>
+          <t>168280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420457</t>
+          <t>419079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451617</t>
+          <t>449460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672200</t>
+          <t>672823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>697388</t>
+          <t>696625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1100826</t>
+          <t>1100633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1139825</t>
+          <t>1140665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>259910</t>
+          <t>258093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>428914</t>
+          <t>427721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>207381</t>
+          <t>209907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>339181</t>
+          <t>339769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>515852</t>
+          <t>529298</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>742708</t>
+          <t>744787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1855067</t>
+          <t>1856260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2024071</t>
+          <t>2025888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1896581</t>
+          <t>1895993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2028381</t>
+          <t>2025855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3777035</t>
+          <t>3774956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4003891</t>
+          <t>3990445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73694</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110747</t>
+          <t>109583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,47 +6243,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>90266</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>75312</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>108641</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>11,4%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90266</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>74000</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>109096</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155510</t>
+          <t>156263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205863</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535876</t>
+          <t>537040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>572929</t>
+          <t>574280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,49 +6356,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>88,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>570197</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>551822</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>585151</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>86,33%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>88,6%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>570197</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>551367</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>586463</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1471</t>
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1101223</t>
+          <t>1098613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1151576</t>
+          <t>1150823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>420411</t>
+          <t>411113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>594206</t>
+          <t>593205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>369431</t>
+          <t>368219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>495681</t>
+          <t>498914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>864370</t>
+          <t>857548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1067165</t>
+          <t>1076679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2850396</t>
+          <t>2851397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3024191</t>
+          <t>3033489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3155459</t>
+          <t>3152226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3281709</t>
+          <t>3282921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6028577</t>
+          <t>6019063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6231372</t>
+          <t>6238194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>75084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112066</t>
+          <t>112583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71436</t>
+          <t>72210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107033</t>
+          <t>106801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156364</t>
+          <t>157021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208801</t>
+          <t>210182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>916385</t>
+          <t>915868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>952500</t>
+          <t>953367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1205838</t>
+          <t>1206070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1241435</t>
+          <t>1240661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2132522</t>
+          <t>2131141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2184959</t>
+          <t>2184302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>288815</t>
+          <t>292783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353665</t>
+          <t>355114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>213227</t>
+          <t>215733</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270300</t>
+          <t>271340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>517212</t>
+          <t>516397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>606109</t>
+          <t>608321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1336152</t>
+          <t>1334703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1401002</t>
+          <t>1397034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1312429</t>
+          <t>1311389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1369502</t>
+          <t>1366996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2666438</t>
+          <t>2664226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2755335</t>
+          <t>2756150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82223</t>
+          <t>84395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119051</t>
+          <t>123149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>74210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108491</t>
+          <t>106605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164580</t>
+          <t>165478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212663</t>
+          <t>216768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>431545</t>
+          <t>427447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468373</t>
+          <t>466201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>366908</t>
+          <t>368794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401620</t>
+          <t>401189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813331</t>
+          <t>809226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>861414</t>
+          <t>860516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>471293</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>558570</t>
+          <t>557285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>384174</t>
+          <t>380718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>457603</t>
+          <t>459893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>873195</t>
+          <t>880119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>991115</t>
+          <t>988972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91824</t>
+          <t>90986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130761</t>
+          <t>130968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106729</t>
+          <t>106362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149603</t>
+          <t>149586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208697</t>
+          <t>208568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>268024</t>
+          <t>265008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>835629</t>
+          <t>835422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>874566</t>
+          <t>875404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1172324</t>
+          <t>1172341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1215198</t>
+          <t>1215565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2020294</t>
+          <t>2023310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2079621</t>
+          <t>2079750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>348782</t>
+          <t>350987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>420695</t>
+          <t>421394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>247980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>309650</t>
+          <t>308545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>614010</t>
+          <t>617533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>707542</t>
+          <t>708220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1529736</t>
+          <t>1529037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1601649</t>
+          <t>1599444</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1432102</t>
+          <t>1433207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1494693</t>
+          <t>1493772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2984642</t>
+          <t>2983964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3078174</t>
+          <t>3074651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87865</t>
+          <t>87197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123623</t>
+          <t>127099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54819</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151710</t>
+          <t>151265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203051</t>
+          <t>202473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>351606</t>
+          <t>348130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387364</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367937</t>
+          <t>368898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400849</t>
+          <t>399487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>727846</t>
+          <t>728424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>779187</t>
+          <t>779632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>554770</t>
+          <t>547354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>642474</t>
+          <t>641957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>427052</t>
+          <t>430685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>512158</t>
+          <t>514693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1007952</t>
+          <t>1012670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1133797</t>
+          <t>1135267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2749576</t>
+          <t>2750093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2837280</t>
+          <t>2844696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3007190</t>
+          <t>3004655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3092296</t>
+          <t>3088663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5777602</t>
+          <t>5776132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5903447</t>
+          <t>5898729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65019</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80325</t>
+          <t>78886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>92893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133675</t>
+          <t>135970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681287</t>
+          <t>681199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>709808</t>
+          <t>708842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>904666</t>
+          <t>906105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>936340</t>
+          <t>936328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1597622</t>
+          <t>1595327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1639644</t>
+          <t>1638404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>284002</t>
+          <t>288089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355385</t>
+          <t>351806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>282702</t>
+          <t>283972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346519</t>
+          <t>351031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589183</t>
+          <t>586730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680347</t>
+          <t>687536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1705587</t>
+          <t>1709166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1776970</t>
+          <t>1772883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1631355</t>
+          <t>1626843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1695172</t>
+          <t>1693902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3358499</t>
+          <t>3351310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3449663</t>
+          <t>3452116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68052</t>
+          <t>69039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104015</t>
+          <t>104534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80249</t>
+          <t>79379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116969</t>
+          <t>115988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161519</t>
+          <t>158483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211068</t>
+          <t>208653</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437247</t>
+          <t>436728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473210</t>
+          <t>472223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425933</t>
+          <t>426914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462653</t>
+          <t>463523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>873096</t>
+          <t>875511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>922645</t>
+          <t>925681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>415727</t>
+          <t>412280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>497857</t>
+          <t>495710</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>433287</t>
+          <t>430801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>513680</t>
+          <t>515419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>868504</t>
+          <t>868824</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>985985</t>
+          <t>983008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2850683</t>
+          <t>2852830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2932813</t>
+          <t>2936260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2992087</t>
+          <t>2990348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3072480</t>
+          <t>3074966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5868321</t>
+          <t>5871298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5985802</t>
+          <t>5985482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>83198</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>65862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94919</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>74760</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58290</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82092</t>
+          <t>88839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>146554</t>
+          <t>157959</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128248</t>
+          <t>137211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168280</t>
+          <t>179155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>436801</t>
+          <t>494378</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419079</t>
+          <t>477392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449460</t>
+          <t>511714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>685558</t>
+          <t>746669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672823</t>
+          <t>732590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>696625</t>
+          <t>757526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1122359</t>
+          <t>1241047</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1100633</t>
+          <t>1219851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1140665</t>
+          <t>1261795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513998</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513998</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513998</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754915</t>
+          <t>821429</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754915</t>
+          <t>821429</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754915</t>
+          <t>821429</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268913</t>
+          <t>1399006</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268913</t>
+          <t>1399006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268913</t>
+          <t>1399006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>364936</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258093</t>
+          <t>362742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>427721</t>
+          <t>454651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>290402</t>
+          <t>320440</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>209907</t>
+          <t>288766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>339769</t>
+          <t>353835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>655339</t>
+          <t>728770</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>529298</t>
+          <t>670940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>744787</t>
+          <t>785712</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1919045</t>
+          <t>1815694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1856260</t>
+          <t>1769373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2025888</t>
+          <t>1861282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1945360</t>
+          <t>1847359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1895993</t>
+          <t>1813964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2025855</t>
+          <t>1879033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3864404</t>
+          <t>3663053</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3774956</t>
+          <t>3606111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3990445</t>
+          <t>3720883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2283981</t>
+          <t>2224024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2283981</t>
+          <t>2224024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2283981</t>
+          <t>2224024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235762</t>
+          <t>2167799</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235762</t>
+          <t>2167799</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235762</t>
+          <t>2167799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4519743</t>
+          <t>4391823</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4519743</t>
+          <t>4391823</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4519743</t>
+          <t>4391823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89884</t>
+          <t>106671</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72343</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109583</t>
+          <t>131281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90266</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>84454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108641</t>
+          <t>119624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180150</t>
+          <t>208391</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156263</t>
+          <t>181676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208473</t>
+          <t>236371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>556739</t>
+          <t>604916</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537040</t>
+          <t>580306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>574280</t>
+          <t>624772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>570197</t>
+          <t>633157</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551822</t>
+          <t>615253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>585151</t>
+          <t>650423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1126936</t>
+          <t>1238073</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1098613</t>
+          <t>1210093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1150823</t>
+          <t>1264788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>411113</t>
+          <t>548029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>593205</t>
+          <t>654372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>450026</t>
+          <t>496921</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>368219</t>
+          <t>461310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>498914</t>
+          <t>538169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>982043</t>
+          <t>1095120</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>857548</t>
+          <t>1026550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1076679</t>
+          <t>1161673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2912585</t>
+          <t>2914989</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2851397</t>
+          <t>2858816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3033489</t>
+          <t>2965159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3201114</t>
+          <t>3227185</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3152226</t>
+          <t>3185937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3282921</t>
+          <t>3262796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6113699</t>
+          <t>6142173</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6019063</t>
+          <t>6075620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6238194</t>
+          <t>6210743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3444602</t>
+          <t>3513188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3444602</t>
+          <t>3513188</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3444602</t>
+          <t>3513188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651140</t>
+          <t>3724106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651140</t>
+          <t>3724106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651140</t>
+          <t>3724106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095742</t>
+          <t>7237293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095742</t>
+          <t>7237293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095742</t>
+          <t>7237293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
